--- a/강의예제/6장_자동화를_위한_표와_피벗_테이블/6장_종합문제.xlsx
+++ b/강의예제/6장_자동화를_위한_표와_피벗_테이블/6장_종합문제.xlsx
@@ -576,13 +576,14 @@
   ② 표로 바꾸기   Ctrl+T, 표 이름을 「지점매출」 로                    (6-01)
   ③ 피벗 만들기   행=지점, 열=연도, 값=매출 합계                      (6-04)
   ④ 계산 필드     이익률 = 이익 / 매출                               (6-11)
-  ⑤ 계산 항목     같은 이익률을 계산 항목으로도 만들어 봅니다           (6-11)
+  ⑤ 비율 열 함정   [자료] 에 이익률 열을 만들어 피벗에 「합계」로 넣어 봅니다 (6-11)
   ⑥ 새로 고침     [자료] 에 한 줄 더하고 Alt+F5                       (6-06)
   ⑦ 최종확인 채우기 [최종확인] 다섯 칸                                —
 ■ 순서를 지켜야 하는 이유
   · ①을 안 하면 필드 목록에 **「2021」 「2022」 가 따로** 뜹니다.
     **「연도」 라는 필드가 없어** 연도별로 못 나눕니다.
   · ④와 ⑤는 **같은 이익률인데 총합계가 다릅니다.** 그것이 이 문제의 핵심입니다.
+    ④ 는 합계끼리 나누고, ⑤ 는 줄마다 나눈 값을 그냥 더합니다.
   · ⑥에서 새로 고침을 안 하면 **옛날 숫자가 그대로** 인쇄됩니다.
 ■ 채점
   노란 칸 = 채울 곳 · 주황 칸 = 답을 적는 곳 · 흰 칸은 자료입니다.</t>
@@ -1218,7 +1219,7 @@
     <row r="9">
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>⑤ 계산 항목으로 내면 총합계가 얼마? (%, 소수 둘째까지)</t>
+          <t>⑤ 원본 이익률 열을 합계로 넣으면 총합계가 얼마? (%, 소수 둘째까지)</t>
         </is>
       </c>
       <c r="C9" s="15" t="n"/>
@@ -1383,7 +1384,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>계산 항목</t>
+          <t>비율 열 함정</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -1393,7 +1394,7 @@
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>같은 곳의 「계산 항목」 으로도 만들어 총합계를 견줍니다. 값이 다릅니다.</t>
+          <t>[자료] F열에 이익률 = 이익/매출 을 만들고 새로 고침. 피벗 값에 이 열을 넣으면 「합계 : 이익률」 — 총합계가 줄별 이익률 25개를 더한 값이 됩니다. (계산 항목으로는 안 됩니다: 계산 항목은 한 필드 안의 항목끼리만 계산합니다.)</t>
         </is>
       </c>
     </row>
